--- a/products/Editors/scenarios/smoke/6. Открытие файла эталона .docx.xlsx
+++ b/products/Editors/scenarios/smoke/6. Открытие файла эталона .docx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Editors\test_cases\smoke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Testing\products\Editors\scenarios\smoke\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971B9155-753D-46E8-898F-96957417FCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8001519-9C0E-4550-AD32-45EF1F374327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
   <si>
     <t>Расположение</t>
   </si>
@@ -63,16 +63,7 @@
     <t>smoke</t>
   </si>
   <si>
-    <t>Установка и обновление</t>
-  </si>
-  <si>
-    <t>Успешно пройдены</t>
-  </si>
-  <si>
     <t>Отображается главное окно редактора, раздел “Главная“ со списком последних документов.</t>
-  </si>
-  <si>
-    <t>В строке состояния кликнуть “По размеру страницы“</t>
   </si>
   <si>
     <t>Масштаб документа изменён.
@@ -89,14 +80,27 @@
 •  визуальные дефекты отсутствуют</t>
   </si>
   <si>
+    <t>В строке состояния кликнуть “По размеру страницы“ 
+&lt;use href="#btn-ic-zoomtopage" class="zoom-int"&gt;&lt;/use&gt;</t>
+  </si>
+  <si>
     <t>Открыть файл с помощью скрипта.
 Mac: open -a 'R7-Office' '/Users/mario/Документы/Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx'
-Windows: "C:\Program Files\R7-Office\Editors\DesktopEditors.exe" "D:\Projects\Editors\test_files\Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx" 
+Windows: "C:\Program Files\R7-Office\Editors\DesktopEditors.exe" "~\Projects\Editors\test_files\Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx" 
 Linux: /opt/r7-office/desktopeditors/DesktopEditors "/home/mario/Документы/Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx"</t>
   </si>
   <si>
-    <t>Ждать 5 секунд
+    <t>Ждать 6 секунд
 Файл “Document_dlya_proverki_vozmozhnostey_tekstovogo_redaktora.docx“ открыт.</t>
+  </si>
+  <si>
+    <t>Тест кейс 5. Проверка кнопок Отменить, Повторить, Сохранить .docx завершен</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>документ остается открытым</t>
   </si>
 </sst>
 </file>
@@ -157,8 +161,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G8" totalsRowShown="0">
-  <autoFilter ref="A1:G8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G9" totalsRowShown="0">
+  <autoFilter ref="A1:G9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Расположение"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Наименование"/>
@@ -457,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="50.6640625" style="2" customWidth="1"/>
@@ -524,16 +528,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -555,9 +559,6 @@
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
@@ -591,16 +592,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -613,17 +614,17 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
@@ -637,16 +638,21 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
